--- a/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_lubrication_system_deviation_monitoring/deviation_monitoring/dsas_g11_lubrication_system_deviation_monitoring_output5.xlsx
+++ b/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_lubrication_system_deviation_monitoring/deviation_monitoring/dsas_g11_lubrication_system_deviation_monitoring_output5.xlsx
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>3.063802542297078e-05</v>
+        <v>0.0002736417868627893</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0002816408393530477</v>
+        <v>0.0006508226358036267</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.006883774150764323</v>
+        <v>0.01248494540991687</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0009418541704941756</v>
+        <v>0.001834234913214951</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.0002544493376691037</v>
+        <v>0.0003271027015624109</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0008731136872116682</v>
+        <v>0.001683521692049697</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2.616448759962506e-05</v>
+        <v>0.0002863787814574499</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0007884187672504638</v>
+        <v>0.001543807400990472</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2.616448759962506e-05</v>
+        <v>0.0002863787814574499</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0007121933392853799</v>
+        <v>0.00141806453903717</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1.993344079101788e-05</v>
+        <v>0.0002258375283346485</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0006429673494359437</v>
+        <v>0.001298841837966918</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.0002513459656121043</v>
+        <v>0.0004382443631220869</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0006038052110535597</v>
+        <v>0.001212782090482435</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2.713826100260486e-05</v>
+        <v>0.0002516656561166316</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0005461385160484642</v>
+        <v>0.001116670447045854</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2.713826100260486e-05</v>
+        <v>0.0002516656561166316</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0004942384905438783</v>
+        <v>0.001030169967952932</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1.200833870030927e-05</v>
+        <v>0.0002311017993442678</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0004460154753595214</v>
+        <v>0.0009502631510920655</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.0001707967791238952</v>
+        <v>0.0002244592145733218</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0004184936057359588</v>
+        <v>0.0008776827574401912</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>3.306046055822523e-05</v>
+        <v>0.0002210177640255654</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0003799502912181855</v>
+        <v>0.0008120162580987285</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0.000255135039250961</v>
+        <v>0.0005340968905718399</v>
       </c>
       <c r="P14" t="n">
-        <v>0.000367468766021463</v>
+        <v>0.0007842243213460397</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>4.587697504640406e-05</v>
+        <v>0.000184929287273505</v>
       </c>
       <c r="P15" t="n">
-        <v>0.000335309586923957</v>
+        <v>0.0007242948179387861</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>1.972541280862636e-05</v>
+        <v>0.0001911321102977804</v>
       </c>
       <c r="P16" t="n">
-        <v>0.000303751169512424</v>
+        <v>0.0006709785471746856</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>3.935310813954037e-05</v>
+        <v>0.000279517064476714</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0002773113633751356</v>
+        <v>0.0006318323989048884</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2.855899531361686e-05</v>
+        <v>0.0002401131610468259</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0002524361265689837</v>
+        <v>0.0005926604751190823</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>1.845251849255814e-05</v>
+        <v>0.000213440893972997</v>
       </c>
       <c r="P19" t="n">
-        <v>0.0002290377657613411</v>
+        <v>0.0005547385170044737</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>1.439643006655873e-05</v>
+        <v>0.000177112859057248</v>
       </c>
       <c r="P20" t="n">
-        <v>0.0002075736321918629</v>
+        <v>0.0005169759512097511</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0.0002112735463704523</v>
+        <v>0.0001459522242756569</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0002079436236097218</v>
+        <v>0.0004798735785163416</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>3.885981782351224e-05</v>
+        <v>0.0003155187283928185</v>
       </c>
       <c r="P22" t="n">
-        <v>0.0001910352430311008</v>
+        <v>0.0004634380935039893</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>0.0001191978916276269</v>
+        <v>0.0004679309065278554</v>
       </c>
       <c r="P23" t="n">
-        <v>0.0001838515078907534</v>
+        <v>0.0004638873748063759</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>2.870293386662836e-05</v>
+        <v>0.0002476745718633341</v>
       </c>
       <c r="P24" t="n">
-        <v>0.0001683366504883409</v>
+        <v>0.0004422660945120717</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>6.624112939843644e-05</v>
+        <v>0.0002001203596890061</v>
       </c>
       <c r="P25" t="n">
-        <v>0.0001581270983793505</v>
+        <v>0.0004180515210297651</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>8.377361249925319e-05</v>
+        <v>0.0001804010491905827</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0001506917497913408</v>
+        <v>0.0003942864738458468</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>0.0002423928309192558</v>
+        <v>0.0004660371696046702</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0001598618579041323</v>
+        <v>0.0004014615434217292</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>3.717257828609576e-05</v>
+        <v>0.0004029843517521475</v>
       </c>
       <c r="P28" t="n">
-        <v>0.0001475929299423286</v>
+        <v>0.000401613824254771</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>4.247567861182297e-05</v>
+        <v>0.0002622168758551881</v>
       </c>
       <c r="P29" t="n">
-        <v>0.0001370812048092781</v>
+        <v>0.0003876741294148128</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>3.027404676907507e-05</v>
+        <v>0.0003046661970941978</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0001264004890052578</v>
+        <v>0.0003793733361827512</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>0.0001279741789172727</v>
+        <v>0.0006395144647992905</v>
       </c>
       <c r="P31" t="n">
-        <v>0.0001265578579964593</v>
+        <v>0.0004053874490444052</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>9.369865379435409e-05</v>
+        <v>0.0005725660193339701</v>
       </c>
       <c r="P32" t="n">
-        <v>0.0001232719375762488</v>
+        <v>0.0004221053060733616</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>4.491707287522802e-05</v>
+        <v>0.0003392003045866375</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0001154364511061467</v>
+        <v>0.0004138148059246892</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>0.0004700956065692347</v>
+        <v>0.0009730700456581184</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0001509023666524555</v>
+        <v>0.0004697403298980321</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>5.545382539615743e-05</v>
+        <v>0.0006818997397954862</v>
       </c>
       <c r="P35" t="n">
-        <v>0.0001413575125268257</v>
+        <v>0.0004909562708877776</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>3.42249436555532e-05</v>
+        <v>0.0005589787539951621</v>
       </c>
       <c r="P36" t="n">
-        <v>0.0001306442556396985</v>
+        <v>0.000497758519198516</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>0.0006072048607809788</v>
+        <v>0.001312915532294766</v>
       </c>
       <c r="P37" t="n">
-        <v>0.0001783003161538266</v>
+        <v>0.0005792742205081411</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>0.0007580763885979765</v>
+        <v>0.001772942845402716</v>
       </c>
       <c r="P38" t="n">
-        <v>0.0002362779233982416</v>
+        <v>0.0006986410829975987</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>0.0008957700598238303</v>
+        <v>0.001836477150135918</v>
       </c>
       <c r="P39" t="n">
-        <v>0.0003022271370408004</v>
+        <v>0.0008124246897114307</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>0.0001814274467319075</v>
+        <v>0.00067999054393961</v>
       </c>
       <c r="P40" t="n">
-        <v>0.0002901471680099111</v>
+        <v>0.0007991812751342487</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>0.000628595602575443</v>
+        <v>0.0009324349055773902</v>
       </c>
       <c r="P41" t="n">
-        <v>0.0003239920114664643</v>
+        <v>0.0008125066381785629</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>0.000210006467287275</v>
+        <v>0.0005150630027326823</v>
       </c>
       <c r="P42" t="n">
-        <v>0.0003125934570485454</v>
+        <v>0.0007827622746339748</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>0.0002396821735562222</v>
+        <v>0.0009557020103765657</v>
       </c>
       <c r="P43" t="n">
-        <v>0.0003053023286993131</v>
+        <v>0.000800056248208234</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>0.0001120273592721553</v>
+        <v>0.0008348696815018963</v>
       </c>
       <c r="P44" t="n">
-        <v>0.0002859748317565973</v>
+        <v>0.0008035375915376003</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>3.104146241292251e-05</v>
+        <v>0.0003707431293636983</v>
       </c>
       <c r="P45" t="n">
-        <v>0.0002604814948222298</v>
+        <v>0.0007602581453202101</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>0.0001697522753334424</v>
+        <v>0.0003032487149257364</v>
       </c>
       <c r="P46" t="n">
-        <v>0.000251408572873351</v>
+        <v>0.0007145572022807627</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>0.0001377440705411001</v>
+        <v>0.0005525084665934007</v>
       </c>
       <c r="P47" t="n">
-        <v>0.0002400421226401259</v>
+        <v>0.0006983523287120264</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>0.0001452919486937955</v>
+        <v>0.0005064426347829666</v>
       </c>
       <c r="P48" t="n">
-        <v>0.0002305671052454929</v>
+        <v>0.0006791613593191205</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>5.677729893129048e-05</v>
+        <v>0.0002400828139541309</v>
       </c>
       <c r="P49" t="n">
-        <v>0.0002131881246140726</v>
+        <v>0.0006352535047826215</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>0.0002753896771526196</v>
+        <v>0.0002410681726480106</v>
       </c>
       <c r="P50" t="n">
-        <v>0.0002194082798679273</v>
+        <v>0.0005958349715691605</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>0.0001343196936166459</v>
+        <v>0.0002156341315866763</v>
       </c>
       <c r="P51" t="n">
-        <v>0.0002108994212427991</v>
+        <v>0.0005578148875709121</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>8.322001945252078e-05</v>
+        <v>0.0002269627751695895</v>
       </c>
       <c r="P52" t="n">
-        <v>0.0001981314810637713</v>
+        <v>0.0005247296763307798</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>0.0001535486725775369</v>
+        <v>0.0004208861608348524</v>
       </c>
       <c r="P53" t="n">
-        <v>0.0001936732002151479</v>
+        <v>0.000514345324781187</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>8.280793378088758e-05</v>
+        <v>0.0003600234863317345</v>
       </c>
       <c r="P54" t="n">
-        <v>0.0001825866735717218</v>
+        <v>0.0004989131409362418</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>0.0001098336735847544</v>
+        <v>0.0001730201333718149</v>
       </c>
       <c r="P55" t="n">
-        <v>0.0001753113735730251</v>
+        <v>0.0004663238401797991</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>0.0002861820208503815</v>
+        <v>0.0005102401797353669</v>
       </c>
       <c r="P56" t="n">
-        <v>0.0001863984383007607</v>
+        <v>0.0004707154741353558</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>9.734752781327104e-05</v>
+        <v>0.0001832405151225685</v>
       </c>
       <c r="P57" t="n">
-        <v>0.0001774933472520117</v>
+        <v>0.000441967978234077</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>0.0002979085520732397</v>
+        <v>0.0006243343977057474</v>
       </c>
       <c r="P58" t="n">
-        <v>0.0001895348677341345</v>
+        <v>0.0004602046201812441</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>7.766546190371437e-05</v>
+        <v>0.0003157807072810351</v>
       </c>
       <c r="P59" t="n">
-        <v>0.0001783479271510925</v>
+        <v>0.0004457622288912232</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>0.0001186643072238683</v>
+        <v>0.0002335038662595433</v>
       </c>
       <c r="P60" t="n">
-        <v>0.0001723795651583701</v>
+        <v>0.0004245363926280552</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>0.0001003258050496302</v>
+        <v>0.0003822078114569017</v>
       </c>
       <c r="P61" t="n">
-        <v>0.0001651741891474961</v>
+        <v>0.0004203035345109399</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>4.039454802636601e-05</v>
+        <v>0.0002482311521654971</v>
       </c>
       <c r="P62" t="n">
-        <v>0.0001526962250353831</v>
+        <v>0.0004030962962763956</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>6.591364311191042e-05</v>
+        <v>0.0001451550059088916</v>
       </c>
       <c r="P63" t="n">
-        <v>0.0001440179668430358</v>
+        <v>0.0003773021672396452</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>0.0006982980786751318</v>
+        <v>0.0007175660242544057</v>
       </c>
       <c r="P64" t="n">
-        <v>0.0001994459780262454</v>
+        <v>0.0004113285529411213</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>0.0004975451329009458</v>
+        <v>0.0006108266404213562</v>
       </c>
       <c r="P65" t="n">
-        <v>0.0002292558935137155</v>
+        <v>0.0004312783616891447</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>0.0006041550279396861</v>
+        <v>0.0006660431462719544</v>
       </c>
       <c r="P66" t="n">
-        <v>0.0002667458069563126</v>
+        <v>0.0004547548401474257</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>2.855899531361686e-05</v>
+        <v>0.0002401131610468259</v>
       </c>
       <c r="P67" t="n">
-        <v>0.000242927125792043</v>
+        <v>0.0004332906722373657</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>2.748045712457876e-05</v>
+        <v>0.0002067286380327541</v>
       </c>
       <c r="P68" t="n">
-        <v>0.0002213824589252966</v>
+        <v>0.0004106344688169045</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>0.000107082358095095</v>
+        <v>0.0003572594901030447</v>
       </c>
       <c r="P69" t="n">
-        <v>0.0002099524488422764</v>
+        <v>0.0004052969709455185</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>3.953702606334104e-05</v>
+        <v>0.0003282281833759781</v>
       </c>
       <c r="P70" t="n">
-        <v>0.0001929109065643829</v>
+        <v>0.0003975900921885645</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>3.193507409378625e-05</v>
+        <v>0.0001956214606036575</v>
       </c>
       <c r="P71" t="n">
-        <v>0.0001768133233173232</v>
+        <v>0.0003773932290300738</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>0.0001515753317930247</v>
+        <v>0.0001450522872038034</v>
       </c>
       <c r="P72" t="n">
-        <v>0.0001742895241648933</v>
+        <v>0.0003541591348474467</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>3.608232202832135e-05</v>
+        <v>0.0001997144450796018</v>
       </c>
       <c r="P73" t="n">
-        <v>0.0001604688039512361</v>
+        <v>0.0003387146658706622</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>3.854613768917479e-05</v>
+        <v>0.0003031672010050006</v>
       </c>
       <c r="P74" t="n">
-        <v>0.00014827653732503</v>
+        <v>0.000335159919384096</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>2.332709429506568e-05</v>
+        <v>0.0002570655853918637</v>
       </c>
       <c r="P75" t="n">
-        <v>0.0001357815930220335</v>
+        <v>0.0003273504859848728</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>0.0008001314604527997</v>
+        <v>0.001115034647014039</v>
       </c>
       <c r="P76" t="n">
-        <v>0.0002022165797651102</v>
+        <v>0.0004061189020877894</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>6.414620655799462e-05</v>
+        <v>0.0003925584875897281</v>
       </c>
       <c r="P77" t="n">
-        <v>0.0001884095424443986</v>
+        <v>0.0004047628606379833</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>4.171726570601362e-05</v>
+        <v>0.000354934818655031</v>
       </c>
       <c r="P78" t="n">
-        <v>0.0001737403147705601</v>
+        <v>0.0003997800564396881</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -4954,10 +4954,10 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>0.0008001314604527997</v>
+        <v>0.001115034647014039</v>
       </c>
       <c r="P79" t="n">
-        <v>0.0002363794293387841</v>
+        <v>0.0004713055154971233</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -5011,10 +5011,10 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>0.0007367373898462146</v>
+        <v>0.001095501870568322</v>
       </c>
       <c r="P80" t="n">
-        <v>0.0002864152253895272</v>
+        <v>0.0005337251510042432</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>0.0001093130736207214</v>
+        <v>0.0004505462834587885</v>
       </c>
       <c r="P81" t="n">
-        <v>0.0002687050102126466</v>
+        <v>0.0005254072642496976</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -5125,14 +5125,14 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>0.004357681907326916</v>
+        <v>0.02531536305244271</v>
       </c>
       <c r="P82" t="n">
-        <v>0.0006776026999240738</v>
+        <v>0.003004402843069001</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Normal (Green)</t>
+          <t>Warning (Yellow) - Operational Drift</t>
         </is>
       </c>
     </row>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>0.0001147628664376067</v>
+        <v>0.0004505730608103183</v>
       </c>
       <c r="P83" t="n">
-        <v>0.0006213187165754271</v>
+        <v>0.002749019864843133</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>0.0001728117112622107</v>
+        <v>0.0004984949767231142</v>
       </c>
       <c r="P84" t="n">
-        <v>0.0005764680160441054</v>
+        <v>0.002523967376031131</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>0.0002867854202766554</v>
+        <v>0.0008352538649959366</v>
       </c>
       <c r="P85" t="n">
-        <v>0.0005474997564673603</v>
+        <v>0.002355096024927611</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>0.0002867854202766554</v>
+        <v>0.0008352538649959366</v>
       </c>
       <c r="P86" t="n">
-        <v>0.0005214283228482899</v>
+        <v>0.002203111808934444</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>0.0002867854202766554</v>
+        <v>0.0008352538649959366</v>
       </c>
       <c r="P87" t="n">
-        <v>0.0004979640325911265</v>
+        <v>0.002066326014540593</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>0.0003507480756909889</v>
+        <v>0.0008089641897519365</v>
       </c>
       <c r="P88" t="n">
-        <v>0.0004832424369011127</v>
+        <v>0.001940589832061727</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>0.0008680052093308482</v>
+        <v>0.001219142425620613</v>
       </c>
       <c r="P89" t="n">
-        <v>0.0005217187141440862</v>
+        <v>0.001868445091417616</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>0.0001971856675300725</v>
+        <v>0.000629590442494525</v>
       </c>
       <c r="P90" t="n">
-        <v>0.0004892654094826849</v>
+        <v>0.001744559626525307</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>0.00133712091352049</v>
+        <v>0.001488628204599459</v>
       </c>
       <c r="P91" t="n">
-        <v>0.0005740509598864653</v>
+        <v>0.001718966484332722</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>0.0008305687776654705</v>
+        <v>0.001277320521752821</v>
       </c>
       <c r="P92" t="n">
-        <v>0.0005997027416643659</v>
+        <v>0.001674801888074731</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -5752,10 +5752,10 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>0.03403517163854677</v>
+        <v>0.04626158454411652</v>
       </c>
       <c r="P93" t="n">
-        <v>0.003943249631352608</v>
+        <v>0.006133480153678914</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -5809,14 +5809,14 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>6.43051833808403e-05</v>
+        <v>0.000455906533340366</v>
       </c>
       <c r="P94" t="n">
-        <v>0.00355535518655543</v>
+        <v>0.005565722791645058</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>Critical (Red) - Systematic Failure</t>
+          <t>Warning (Yellow) - Operational Drift</t>
         </is>
       </c>
     </row>
@@ -5866,14 +5866,14 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>0.0003637186992620017</v>
+        <v>0.0007490673920956127</v>
       </c>
       <c r="P95" t="n">
-        <v>0.003236191537826088</v>
+        <v>0.005084057251690114</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>Critical (Red) - Systematic Failure</t>
+          <t>Warning (Yellow) - Operational Drift</t>
         </is>
       </c>
     </row>
@@ -5923,14 +5923,14 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>0.0002902535375198763</v>
+        <v>0.0007470702114224599</v>
       </c>
       <c r="P96" t="n">
-        <v>0.002941597737795466</v>
+        <v>0.004650358547663348</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Critical (Red) - Systematic Failure</t>
+          <t>Warning (Yellow) - Operational Drift</t>
         </is>
       </c>
     </row>
@@ -5980,10 +5980,10 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>0.0002890244677010319</v>
+        <v>0.0008069116413332027</v>
       </c>
       <c r="P97" t="n">
-        <v>0.002676340410786023</v>
+        <v>0.004266013857030334</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>0.001085963683597696</v>
+        <v>0.001954610372474557</v>
       </c>
       <c r="P98" t="n">
-        <v>0.00251730273806719</v>
+        <v>0.004034873508574756</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -6094,10 +6094,10 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>0.0007948668402244667</v>
+        <v>0.002273365756503451</v>
       </c>
       <c r="P99" t="n">
-        <v>0.002345059148282918</v>
+        <v>0.003858722733367625</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -6151,10 +6151,10 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>8.728870927941788e-05</v>
+        <v>0.0005855280835118089</v>
       </c>
       <c r="P100" t="n">
-        <v>0.002119282104382568</v>
+        <v>0.003531403268382043</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -6208,10 +6208,10 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>0.0007490093679816081</v>
+        <v>0.002200769276222151</v>
       </c>
       <c r="P101" t="n">
-        <v>0.001982254830742471</v>
+        <v>0.003398339869166054</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -6265,10 +6265,10 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>5.101795508968328e-05</v>
+        <v>0.000493661894467872</v>
       </c>
       <c r="P102" t="n">
-        <v>0.001789131143177193</v>
+        <v>0.003107872071696235</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -6322,10 +6322,10 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>0.000308681760645793</v>
+        <v>0.0012053862505937</v>
       </c>
       <c r="P103" t="n">
-        <v>0.001641086204924053</v>
+        <v>0.002917623489585982</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -6379,14 +6379,14 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>0.0007965503200199804</v>
+        <v>0.002622973922819649</v>
       </c>
       <c r="P104" t="n">
-        <v>0.001556632616433646</v>
+        <v>0.002888158532909349</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>

--- a/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_lubrication_system_deviation_monitoring/deviation_monitoring/dsas_g11_lubrication_system_deviation_monitoring_output5.xlsx
+++ b/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_lubrication_system_deviation_monitoring/deviation_monitoring/dsas_g11_lubrication_system_deviation_monitoring_output5.xlsx
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.0002736417868627893</v>
+        <v>0.0001414823043308068</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0006508226358036267</v>
+        <v>0.0004487130592512936</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.01248494540991687</v>
+        <v>0.01216501308990081</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001834234913214951</v>
+        <v>0.001620343062316246</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.0003271027015624109</v>
+        <v>0.0001969781257037679</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001683521692049697</v>
+        <v>0.001478006568654998</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.0002863787814574499</v>
+        <v>0.0001713633101099438</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001543807400990472</v>
+        <v>0.001347342242800492</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.0002863787814574499</v>
+        <v>0.0001713633101099438</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00141806453903717</v>
+        <v>0.001229744349531437</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.0002258375283346485</v>
+        <v>0.0001228082440376191</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001298841837966918</v>
+        <v>0.001119050738982056</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.0004382443631220869</v>
+        <v>0.0003804643407239472</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001212782090482435</v>
+        <v>0.001045192099156245</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.0002516656561166316</v>
+        <v>0.0001821480603190319</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001116670447045854</v>
+        <v>0.0009588876952725235</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0.0002516656561166316</v>
+        <v>0.0001821480603190319</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001030169967952932</v>
+        <v>0.0008812137317771744</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0.0002311017993442678</v>
+        <v>0.0001199472673269248</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0009502631510920655</v>
+        <v>0.0008050870853321495</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.0002244592145733218</v>
+        <v>0.0001001962532138793</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0008776827574401912</v>
+        <v>0.0007345980021203224</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0.0002210177640255654</v>
+        <v>0.0001462416980669598</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0008120162580987285</v>
+        <v>0.0006757623717149862</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0.0005340968905718399</v>
+        <v>0.0007827160174716752</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0007842243213460397</v>
+        <v>0.0006864577362906551</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.000184929287273505</v>
+        <v>0.0002659780361027668</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0007242948179387861</v>
+        <v>0.0006444097662718662</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.0001911321102977804</v>
+        <v>0.0002749253629934748</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0006709785471746856</v>
+        <v>0.0006074613259440272</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0.000279517064476714</v>
+        <v>0.0002323724841743915</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0006318323989048884</v>
+        <v>0.0005699524417670636</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0.0002401131610468259</v>
+        <v>0.0001600940623978999</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0005926604751190823</v>
+        <v>0.0005289666038301472</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0.000213440893972997</v>
+        <v>0.0002923028504295874</v>
       </c>
       <c r="P19" t="n">
-        <v>0.0005547385170044737</v>
+        <v>0.0005053002284900912</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0.000177112859057248</v>
+        <v>0.0002113865136482732</v>
       </c>
       <c r="P20" t="n">
-        <v>0.0005169759512097511</v>
+        <v>0.0004759088570059094</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0.0001459522242756569</v>
+        <v>0.0001058194896867724</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0004798735785163416</v>
+        <v>0.0004388999202739956</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>0.0003155187283928185</v>
+        <v>0.0002563231725346251</v>
       </c>
       <c r="P22" t="n">
-        <v>0.0004634380935039893</v>
+        <v>0.0004206422455000585</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>0.0004679309065278554</v>
+        <v>0.0004769983520022667</v>
       </c>
       <c r="P23" t="n">
-        <v>0.0004638873748063759</v>
+        <v>0.0004262778561502794</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>0.0002476745718633341</v>
+        <v>8.186796523014574e-05</v>
       </c>
       <c r="P24" t="n">
-        <v>0.0004422660945120717</v>
+        <v>0.000391836867058266</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>0.0002001203596890061</v>
+        <v>2.871451156222401e-05</v>
       </c>
       <c r="P25" t="n">
-        <v>0.0004180515210297651</v>
+        <v>0.0003555246315086618</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>0.0001804010491905827</v>
+        <v>9.790649533518748e-05</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0003942864738458468</v>
+        <v>0.0003297628178913143</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>0.0004660371696046702</v>
+        <v>0.000727267401122221</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0004014615434217292</v>
+        <v>0.0003695132762144051</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>0.0004029843517521475</v>
+        <v>0.0002291021248382113</v>
       </c>
       <c r="P28" t="n">
-        <v>0.000401613824254771</v>
+        <v>0.0003554721610767857</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>0.0002622168758551881</v>
+        <v>6.004562698121841e-05</v>
       </c>
       <c r="P29" t="n">
-        <v>0.0003876741294148128</v>
+        <v>0.0003259295076672289</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>0.0003046661970941978</v>
+        <v>9.560233115197299e-05</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0003793733361827512</v>
+        <v>0.0003028967900157033</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>0.0006395144647992905</v>
+        <v>0.0003648748725466033</v>
       </c>
       <c r="P31" t="n">
-        <v>0.0004053874490444052</v>
+        <v>0.0003090945982687933</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0.0005725660193339701</v>
+        <v>0.0002807556300594837</v>
       </c>
       <c r="P32" t="n">
-        <v>0.0004221053060733616</v>
+        <v>0.0003062607014478623</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>0.0003392003045866375</v>
+        <v>0.0001630404622613453</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0004138148059246892</v>
+        <v>0.0002919386775292106</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>0.0009730700456581184</v>
+        <v>0.001115647323914348</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0004697403298980321</v>
+        <v>0.0003743095421677244</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>0.0006818997397954862</v>
+        <v>0.0002343374824359351</v>
       </c>
       <c r="P35" t="n">
-        <v>0.0004909562708877776</v>
+        <v>0.0003603123361945455</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>0.0005589787539951621</v>
+        <v>0.0001163398296791172</v>
       </c>
       <c r="P36" t="n">
-        <v>0.000497758519198516</v>
+        <v>0.0003359150855430026</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>0.001312915532294766</v>
+        <v>0.001190203638697211</v>
       </c>
       <c r="P37" t="n">
-        <v>0.0005792742205081411</v>
+        <v>0.0004213439408584235</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>0.001772942845402716</v>
+        <v>0.002677683584289662</v>
       </c>
       <c r="P38" t="n">
-        <v>0.0006986410829975987</v>
+        <v>0.0006469779052015474</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>0.001836477150135918</v>
+        <v>0.002858118103920399</v>
       </c>
       <c r="P39" t="n">
-        <v>0.0008124246897114307</v>
+        <v>0.0008680919250734325</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>0.00067999054393961</v>
+        <v>0.0004885728991952141</v>
       </c>
       <c r="P40" t="n">
-        <v>0.0007991812751342487</v>
+        <v>0.0008301400224856107</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>0.0009324349055773902</v>
+        <v>0.001186919307222395</v>
       </c>
       <c r="P41" t="n">
-        <v>0.0008125066381785629</v>
+        <v>0.0008658179509592891</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>0.0005150630027326823</v>
+        <v>0.0005427781639627297</v>
       </c>
       <c r="P42" t="n">
-        <v>0.0007827622746339748</v>
+        <v>0.0008335139722596333</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>0.0009557020103765657</v>
+        <v>0.0002931696976277989</v>
       </c>
       <c r="P43" t="n">
-        <v>0.000800056248208234</v>
+        <v>0.0007794795447964498</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>0.0008348696815018963</v>
+        <v>0.0001665073384235999</v>
       </c>
       <c r="P44" t="n">
-        <v>0.0008035375915376003</v>
+        <v>0.0007181823241591647</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>0.0003707431293636983</v>
+        <v>8.858231047362435e-05</v>
       </c>
       <c r="P45" t="n">
-        <v>0.0007602581453202101</v>
+        <v>0.0006552223227906107</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>0.0003032487149257364</v>
+        <v>0.0002600970417074252</v>
       </c>
       <c r="P46" t="n">
-        <v>0.0007145572022807627</v>
+        <v>0.0006157097946822921</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>0.0005525084665934007</v>
+        <v>0.0003565843580186047</v>
       </c>
       <c r="P47" t="n">
-        <v>0.0006983523287120264</v>
+        <v>0.0005897972510159233</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>0.0005064426347829666</v>
+        <v>0.0003673995085255636</v>
       </c>
       <c r="P48" t="n">
-        <v>0.0006791613593191205</v>
+        <v>0.0005675574767668874</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>0.0002400828139541309</v>
+        <v>5.591115030850607e-05</v>
       </c>
       <c r="P49" t="n">
-        <v>0.0006352535047826215</v>
+        <v>0.0005163928441210492</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>0.0002410681726480106</v>
+        <v>0.0002715539734547173</v>
       </c>
       <c r="P50" t="n">
-        <v>0.0005958349715691605</v>
+        <v>0.000491908957054416</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>0.0002156341315866763</v>
+        <v>6.286697790936013e-05</v>
       </c>
       <c r="P51" t="n">
-        <v>0.0005578148875709121</v>
+        <v>0.0004490047591399104</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>0.0002269627751695895</v>
+        <v>6.666131177388869e-05</v>
       </c>
       <c r="P52" t="n">
-        <v>0.0005247296763307798</v>
+        <v>0.0004107704144033082</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>0.0004208861608348524</v>
+        <v>0.0002681979611802059</v>
       </c>
       <c r="P53" t="n">
-        <v>0.000514345324781187</v>
+        <v>0.0003965131690809979</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>0.0003600234863317345</v>
+        <v>0.0001717464486045802</v>
       </c>
       <c r="P54" t="n">
-        <v>0.0004989131409362418</v>
+        <v>0.0003740364970333562</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>0.0001730201333718149</v>
+        <v>7.267860716644134e-05</v>
       </c>
       <c r="P55" t="n">
-        <v>0.0004663238401797991</v>
+        <v>0.0003439007080466647</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>0.0005102401797353669</v>
+        <v>0.0004567608011139287</v>
       </c>
       <c r="P56" t="n">
-        <v>0.0004707154741353558</v>
+        <v>0.0003551867173533911</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>0.0001832405151225685</v>
+        <v>4.089629663119978e-05</v>
       </c>
       <c r="P57" t="n">
-        <v>0.000441967978234077</v>
+        <v>0.0003237576752811719</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>0.0006243343977057474</v>
+        <v>0.0005797560900767461</v>
       </c>
       <c r="P58" t="n">
-        <v>0.0004602046201812441</v>
+        <v>0.0003493575167607294</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>0.0003157807072810351</v>
+        <v>0.000101453527292245</v>
       </c>
       <c r="P59" t="n">
-        <v>0.0004457622288912232</v>
+        <v>0.000324567117813881</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>0.0002335038662595433</v>
+        <v>0.0002928916133895986</v>
       </c>
       <c r="P60" t="n">
-        <v>0.0004245363926280552</v>
+        <v>0.0003213995673714528</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>0.0003822078114569017</v>
+        <v>0.0004153549986769738</v>
       </c>
       <c r="P61" t="n">
-        <v>0.0004203035345109399</v>
+        <v>0.0003307951105020048</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>0.0002482311521654971</v>
+        <v>0.0002033605237313423</v>
       </c>
       <c r="P62" t="n">
-        <v>0.0004030962962763956</v>
+        <v>0.0003180516518249386</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>0.0001451550059088916</v>
+        <v>3.890194615409536e-05</v>
       </c>
       <c r="P63" t="n">
-        <v>0.0003773021672396452</v>
+        <v>0.0002901366812578542</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>0.0007175660242544057</v>
+        <v>0.001125272492161835</v>
       </c>
       <c r="P64" t="n">
-        <v>0.0004113285529411213</v>
+        <v>0.0003736502623482523</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>0.0006108266404213562</v>
+        <v>0.0008924359780702212</v>
       </c>
       <c r="P65" t="n">
-        <v>0.0004312783616891447</v>
+        <v>0.0004255288339204492</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>0.0006660431462719544</v>
+        <v>0.00103067721261297</v>
       </c>
       <c r="P66" t="n">
-        <v>0.0004547548401474257</v>
+        <v>0.0004860436717897014</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>0.0002401131610468259</v>
+        <v>0.0001600940623978999</v>
       </c>
       <c r="P67" t="n">
-        <v>0.0004332906722373657</v>
+        <v>0.0004534487108505212</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>0.0002067286380327541</v>
+        <v>0.0001035736075748171</v>
       </c>
       <c r="P68" t="n">
-        <v>0.0004106344688169045</v>
+        <v>0.0004184612005229507</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>0.0003572594901030447</v>
+        <v>0.0003934177767448472</v>
       </c>
       <c r="P69" t="n">
-        <v>0.0004052969709455185</v>
+        <v>0.0004159568581451404</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>0.0003282281833759781</v>
+        <v>0.0002644714569130893</v>
       </c>
       <c r="P70" t="n">
-        <v>0.0003975900921885645</v>
+        <v>0.0004008083180219353</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>0.0001956214606036575</v>
+        <v>6.664841491776874e-05</v>
       </c>
       <c r="P71" t="n">
-        <v>0.0003773932290300738</v>
+        <v>0.0003673923277115186</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>0.0001450522872038034</v>
+        <v>5.545319575028834e-05</v>
       </c>
       <c r="P72" t="n">
-        <v>0.0003541591348474467</v>
+        <v>0.0003361984145153956</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>0.0001997144450796018</v>
+        <v>8.060580253310545e-05</v>
       </c>
       <c r="P73" t="n">
-        <v>0.0003387146658706622</v>
+        <v>0.0003106391533171666</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>0.0003031672010050006</v>
+        <v>0.0002486313176723689</v>
       </c>
       <c r="P74" t="n">
-        <v>0.000335159919384096</v>
+        <v>0.0003044383697526868</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>0.0002570655853918637</v>
+        <v>0.0001254105886267228</v>
       </c>
       <c r="P75" t="n">
-        <v>0.0003273504859848728</v>
+        <v>0.0002865355916400904</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>0.001115034647014039</v>
+        <v>0.001961278281326441</v>
       </c>
       <c r="P76" t="n">
-        <v>0.0004061189020877894</v>
+        <v>0.0004540098606087255</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>0.0003925584875897281</v>
+        <v>0.0003694970981823562</v>
       </c>
       <c r="P77" t="n">
-        <v>0.0004047628606379833</v>
+        <v>0.0004455585843660885</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>0.000354934818655031</v>
+        <v>0.0002792325328081148</v>
       </c>
       <c r="P78" t="n">
-        <v>0.0003997800564396881</v>
+        <v>0.0004289259792102912</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -4954,10 +4954,10 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>0.001115034647014039</v>
+        <v>0.001961278281326441</v>
       </c>
       <c r="P79" t="n">
-        <v>0.0004713055154971233</v>
+        <v>0.0005821612094219062</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -5011,10 +5011,10 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>0.001095501870568322</v>
+        <v>0.002098427298061361</v>
       </c>
       <c r="P80" t="n">
-        <v>0.0005337251510042432</v>
+        <v>0.0007337878182858518</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>0.0004505462834587885</v>
+        <v>0.0007087202924689472</v>
       </c>
       <c r="P81" t="n">
-        <v>0.0005254072642496976</v>
+        <v>0.0007312810657041613</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -5125,14 +5125,14 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>0.02531536305244271</v>
+        <v>0.00707632781723149</v>
       </c>
       <c r="P82" t="n">
-        <v>0.003004402843069001</v>
+        <v>0.001365785740856894</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>0.0004505730608103183</v>
+        <v>0.0005096031356552314</v>
       </c>
       <c r="P83" t="n">
-        <v>0.002749019864843133</v>
+        <v>0.001280167480336728</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>0.0004984949767231142</v>
+        <v>0.0006091825899259511</v>
       </c>
       <c r="P84" t="n">
-        <v>0.002523967376031131</v>
+        <v>0.00121306899129565</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>0.0008352538649959366</v>
+        <v>0.000971834656724776</v>
       </c>
       <c r="P85" t="n">
-        <v>0.002355096024927611</v>
+        <v>0.001188945557838563</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>0.0008352538649959366</v>
+        <v>0.000971834656724776</v>
       </c>
       <c r="P86" t="n">
-        <v>0.002203111808934444</v>
+        <v>0.001167234467727184</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>0.0008352538649959366</v>
+        <v>0.000971834656724776</v>
       </c>
       <c r="P87" t="n">
-        <v>0.002066326014540593</v>
+        <v>0.001147694486626943</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>0.0008089641897519365</v>
+        <v>0.0008886957531145934</v>
       </c>
       <c r="P88" t="n">
-        <v>0.001940589832061727</v>
+        <v>0.001121794613275709</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>0.001219142425620613</v>
+        <v>0.001862926586522071</v>
       </c>
       <c r="P89" t="n">
-        <v>0.001868445091417616</v>
+        <v>0.001195907810600345</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>0.000629590442494525</v>
+        <v>0.0007584509812032538</v>
       </c>
       <c r="P90" t="n">
-        <v>0.001744559626525307</v>
+        <v>0.001152162127660636</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>0.001488628204599459</v>
+        <v>0.002778125243015595</v>
       </c>
       <c r="P91" t="n">
-        <v>0.001718966484332722</v>
+        <v>0.001314758439196132</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>0.001277320521752821</v>
+        <v>0.00203404783032805</v>
       </c>
       <c r="P92" t="n">
-        <v>0.001674801888074731</v>
+        <v>0.001386687378309324</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -5752,14 +5752,14 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>0.04626158454411652</v>
+        <v>0.03109636658859283</v>
       </c>
       <c r="P93" t="n">
-        <v>0.006133480153678914</v>
+        <v>0.004357655299337676</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>Critical (Red) - Systematic Failure</t>
+          <t>Warning (Yellow) - Operational Drift</t>
         </is>
       </c>
     </row>
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>0.000455906533340366</v>
+        <v>0.0003842513661085351</v>
       </c>
       <c r="P94" t="n">
-        <v>0.005565722791645058</v>
+        <v>0.003960314906014762</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>0.0007490673920956127</v>
+        <v>0.0009381860093888623</v>
       </c>
       <c r="P95" t="n">
-        <v>0.005084057251690114</v>
+        <v>0.003658102016352172</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>0.0007470702114224599</v>
+        <v>0.0009813474788161771</v>
       </c>
       <c r="P96" t="n">
-        <v>0.004650358547663348</v>
+        <v>0.003390426562598572</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -5980,10 +5980,10 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>0.0008069116413332027</v>
+        <v>0.0009846289281869986</v>
       </c>
       <c r="P97" t="n">
-        <v>0.004266013857030334</v>
+        <v>0.003149846799157415</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>0.001954610372474557</v>
+        <v>0.001979909984406645</v>
       </c>
       <c r="P98" t="n">
-        <v>0.004034873508574756</v>
+        <v>0.003032853117682338</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -6094,10 +6094,10 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>0.002273365756503451</v>
+        <v>0.002302677225837705</v>
       </c>
       <c r="P99" t="n">
-        <v>0.003858722733367625</v>
+        <v>0.002959835528497874</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -6151,10 +6151,10 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>0.0005855280835118089</v>
+        <v>0.0004491054924989815</v>
       </c>
       <c r="P100" t="n">
-        <v>0.003531403268382043</v>
+        <v>0.002708762524897985</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -6208,10 +6208,10 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>0.002200769276222151</v>
+        <v>0.002112479698950178</v>
       </c>
       <c r="P101" t="n">
-        <v>0.003398339869166054</v>
+        <v>0.002649134242303204</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -6265,10 +6265,10 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>0.000493661894467872</v>
+        <v>0.0003144861457336144</v>
       </c>
       <c r="P102" t="n">
-        <v>0.003107872071696235</v>
+        <v>0.002415669432646245</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -6322,10 +6322,10 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>0.0012053862505937</v>
+        <v>0.0008607688138135464</v>
       </c>
       <c r="P103" t="n">
-        <v>0.002917623489585982</v>
+        <v>0.002260179370762975</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -6379,14 +6379,14 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>0.002622973922819649</v>
+        <v>0.002489904029745858</v>
       </c>
       <c r="P104" t="n">
-        <v>0.002888158532909349</v>
+        <v>0.002283151836661263</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Normal (Green)</t>
+          <t>Warning (Yellow) - Operational Drift</t>
         </is>
       </c>
     </row>
